--- a/Greenhub/results/phase7_scenario_comparison.xlsx
+++ b/Greenhub/results/phase7_scenario_comparison.xlsx
@@ -648,7 +648,7 @@
         <v>243.6194401251267</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -719,7 +719,7 @@
         <v>243.6194401251267</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0.06440653971565025</v>
@@ -790,7 +790,7 @@
         <v>243.6194401251267</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
         <v>243.6194401251267</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0.06440653971565025</v>
@@ -932,10 +932,10 @@
         <v>243.6194401251267</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.06910842193494444</v>
+        <v>0.06910842193494443</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
@@ -1003,7 +1003,7 @@
         <v>243.6194401251267</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
@@ -1074,7 +1074,7 @@
         <v>243.6194401251267</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0.06440653971565025</v>
@@ -1333,25 +1333,25 @@
         <v>0</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
     </row>
     <row r="6">
@@ -1376,7 +1376,7 @@
         <v>0.06440653971565025</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.06910842193494444</v>
+        <v>0.06910842193494443</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>0</v>

--- a/Greenhub/results/phase7_scenario_comparison.xlsx
+++ b/Greenhub/results/phase7_scenario_comparison.xlsx
@@ -453,8 +453,8 @@
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="19" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
     <col width="27" customWidth="1" min="17" max="17"/>
     <col width="29" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>243.6194401251267</v>
+        <v>243.6194401251268</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>243.6194401251267</v>
+        <v>243.6194401251268</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3.20719178564155</v>
+        <v>3.207191785641549</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -675,7 +675,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1542923120792469</v>
+        <v>0.154292312079247</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>0</v>
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>243.6194401251267</v>
+        <v>243.6194401251268</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3.20719178564155</v>
+        <v>3.207191785641549</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0.06440653971565025</v>
@@ -746,7 +746,7 @@
         <v>0.02404122483394852</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1672814267144845</v>
+        <v>0.1672814267144846</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>243.6194401251267</v>
+        <v>243.6194401251268</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3.20719178564155</v>
+        <v>3.207191785641549</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
@@ -820,10 +820,10 @@
         <v>0.1592944937128782</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>7.036627502664713</v>
+        <v>7.036627502664714</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>7.036627502664713</v>
+        <v>7.036627502664714</v>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>243.6194401251267</v>
+        <v>243.6194401251268</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3.20719178564155</v>
+        <v>3.207191785641549</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0.06440653971565025</v>
@@ -891,10 +891,10 @@
         <v>0.1722832689345142</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>7.036149712795237</v>
+        <v>7.036149712795238</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>7.036149712795237</v>
+        <v>7.036149712795238</v>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>243.6194401251267</v>
+        <v>243.6194401251268</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>3.20719178564155</v>
+        <v>3.207191785641549</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.06910842193494443</v>
+        <v>0.06910842193494444</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>243.6194401251267</v>
+        <v>243.6194401251268</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3.20719178564155</v>
+        <v>3.207191785641549</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>243.6194401251267</v>
+        <v>243.6194401251268</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3.20719178564155</v>
+        <v>3.207191785641549</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0.06440653971565025</v>
@@ -1101,7 +1101,7 @@
         <v>4.105541458352352</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>3.235798486864002</v>
+        <v>3.235798486864004</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>144.386734532246</v>
@@ -1299,28 +1299,28 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>243.6194401251267</v>
+        <v>243.6194401251268</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>243.6194401251267</v>
+        <v>243.6194401251268</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>243.6194401251267</v>
+        <v>243.6194401251268</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>243.6194401251267</v>
+        <v>243.6194401251268</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>243.6194401251267</v>
+        <v>243.6194401251268</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>243.6194401251267</v>
+        <v>243.6194401251268</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>243.6194401251267</v>
+        <v>243.6194401251268</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>243.6194401251267</v>
+        <v>243.6194401251268</v>
       </c>
     </row>
     <row r="5">
@@ -1333,25 +1333,25 @@
         <v>0</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3.20719178564155</v>
+        <v>3.207191785641549</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3.20719178564155</v>
+        <v>3.207191785641549</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3.20719178564155</v>
+        <v>3.207191785641549</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3.20719178564155</v>
+        <v>3.207191785641549</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>3.20719178564155</v>
+        <v>3.207191785641549</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>3.20719178564155</v>
+        <v>3.207191785641549</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3.20719178564155</v>
+        <v>3.207191785641549</v>
       </c>
     </row>
     <row r="6">
@@ -1376,7 +1376,7 @@
         <v>0.06440653971565025</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.06910842193494443</v>
+        <v>0.06910842193494444</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>0</v>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.1542923120792469</v>
+        <v>0.154292312079247</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.1672814267144845</v>
+        <v>0.1672814267144846</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0.1592944937128782</v>
@@ -1630,7 +1630,7 @@
         <v>0.155246328937737</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3.235798486864002</v>
+        <v>3.235798486864004</v>
       </c>
     </row>
     <row r="15">
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>7.036627502664713</v>
+        <v>7.036627502664714</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>7.036149712795237</v>
+        <v>7.036149712795238</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0</v>
@@ -1680,10 +1680,10 @@
         <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>7.036627502664713</v>
+        <v>7.036627502664714</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>7.036149712795237</v>
+        <v>7.036149712795238</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>

--- a/Greenhub/results/phase7_scenario_comparison.xlsx
+++ b/Greenhub/results/phase7_scenario_comparison.xlsx
@@ -453,8 +453,8 @@
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
     <col width="27" customWidth="1" min="17" max="17"/>
     <col width="29" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>243.6194401251268</v>
+        <v>243.6194401251267</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>243.6194401251268</v>
+        <v>243.6194401251267</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -675,7 +675,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.154292312079247</v>
+        <v>0.1542923120792469</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>0</v>
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>243.6194401251268</v>
+        <v>243.6194401251267</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0.06440653971565025</v>
@@ -746,7 +746,7 @@
         <v>0.02404122483394852</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1672814267144846</v>
+        <v>0.1672814267144845</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>243.6194401251268</v>
+        <v>243.6194401251267</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
@@ -820,10 +820,10 @@
         <v>0.1592944937128782</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>7.036627502664714</v>
+        <v>7.036627502664713</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>7.036627502664714</v>
+        <v>7.036627502664713</v>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>243.6194401251268</v>
+        <v>243.6194401251267</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0.06440653971565025</v>
@@ -891,10 +891,10 @@
         <v>0.1722832689345142</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>7.036149712795238</v>
+        <v>7.036149712795237</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>7.036149712795238</v>
+        <v>7.036149712795237</v>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>243.6194401251268</v>
+        <v>243.6194401251267</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.06910842193494444</v>
+        <v>0.06910842193494443</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>243.6194401251268</v>
+        <v>243.6194401251267</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>243.6194401251268</v>
+        <v>243.6194401251267</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0.06440653971565025</v>
@@ -1101,7 +1101,7 @@
         <v>4.105541458352352</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>3.235798486864004</v>
+        <v>3.235798486864002</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>144.386734532246</v>
@@ -1299,28 +1299,28 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>243.6194401251268</v>
+        <v>243.6194401251267</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>243.6194401251268</v>
+        <v>243.6194401251267</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>243.6194401251268</v>
+        <v>243.6194401251267</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>243.6194401251268</v>
+        <v>243.6194401251267</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>243.6194401251268</v>
+        <v>243.6194401251267</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>243.6194401251268</v>
+        <v>243.6194401251267</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>243.6194401251268</v>
+        <v>243.6194401251267</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>243.6194401251268</v>
+        <v>243.6194401251267</v>
       </c>
     </row>
     <row r="5">
@@ -1333,25 +1333,25 @@
         <v>0</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3.207191785641549</v>
+        <v>3.20719178564155</v>
       </c>
     </row>
     <row r="6">
@@ -1376,7 +1376,7 @@
         <v>0.06440653971565025</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.06910842193494444</v>
+        <v>0.06910842193494443</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>0</v>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.154292312079247</v>
+        <v>0.1542923120792469</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.1672814267144846</v>
+        <v>0.1672814267144845</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0.1592944937128782</v>
@@ -1630,7 +1630,7 @@
         <v>0.155246328937737</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3.235798486864004</v>
+        <v>3.235798486864002</v>
       </c>
     </row>
     <row r="15">
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>7.036627502664714</v>
+        <v>7.036627502664713</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>7.036149712795238</v>
+        <v>7.036149712795237</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0</v>
@@ -1680,10 +1680,10 @@
         <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>7.036627502664714</v>
+        <v>7.036627502664713</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>7.036149712795238</v>
+        <v>7.036149712795237</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>
